--- a/Employee_Reports_wi48/Mohamed Shafras Jawlangull Q0517.xlsx
+++ b/Employee_Reports_wi48/Mohamed Shafras Jawlangull Q0517.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1426,9 +1426,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1440,11 +1452,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1489,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1526,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1563,11 +1575,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1612,11 +1624,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1649,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2072,7 +2084,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7943</v>
+        <v>7940</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2095,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2167,7 +2179,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2196,7 +2208,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2237,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2254,7 +2266,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2283,7 +2295,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2312,7 +2324,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2353,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2370,7 +2382,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2411,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2428,7 +2440,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2448,16 +2460,16 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2477,16 +2489,16 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2506,16 +2518,16 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2535,16 +2547,16 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2573,7 +2585,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2602,7 +2614,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2610,6 +2622,35 @@
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
